--- a/selenium_model/APPIUM_E2E_350_REPORT.xlsx
+++ b/selenium_model/APPIUM_E2E_350_REPORT.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F344" t="n">
